--- a/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
+++ b/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
@@ -17,10 +17,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_C1" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_C2" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_C3" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_D1" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_E1" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_E2" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_E3" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_C4" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_D1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_E1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_E2" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix_Table_E3" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,10 +30,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +46,37 @@
       <b val="1"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -57,16 +88,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF2F8"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -80,37 +111,94 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
     <border>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,12 +563,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -491,55 +579,55 @@
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Obs</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>P25</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P50</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>P75</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -562,46 +650,48 @@
       <c r="G2" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="4" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ln(price)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="6" t="n">
         <v>521</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="7" t="n">
         <v>-0.98</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>1.696</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="7" t="n">
         <v>-4.605</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="7" t="n">
         <v>-2.303</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="7" t="n">
         <v>-1.386</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="7" t="n">
         <v>5.011</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -609,205 +699,207 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="20.72" customWidth="1" min="1" max="1"/>
+    <col width="35.84" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Statistic</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>A. Node coverage</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Products (with price)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>521</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>A. Node coverage</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Suppliers (connected to priced products)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>A. Node coverage</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>src industries (connected to priced products)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>A. Node coverage</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>app industries (connected to priced products)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>B. Edge coverage</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Triples: provide_data</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>521</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>B. Edge coverage</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Triples: source_industry</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>B. Edge coverage</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Triples: applied_to</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>764</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>C. Degree &amp; label sparsity</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Products per supplier (mean; P25/P50/P75; max)</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>6.058; 1/2/4; 145</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>C. Degree &amp; label sparsity</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>App labels per product (mean; P25/P50/P75; max)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>1.466; 1/1/2; 6</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>C. Degree &amp; label sparsity</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Src labels per product (mean; P25/P50/P75; max)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>1.161; 1/1/1; 15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -815,12 +907,295 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Panel A. Posted-price availability and analytical-sample construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Sample category</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Share of KG universe</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Share of price-observed listings</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Broader KG universe</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>6686</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Listings with standardizable posted-price information</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>555</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Listings without standardizable posted-price information</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>6131</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Price-observed listings excluded by price cleaning</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Final price-modeling sample</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>521</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="E7" s="21" t="n"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Panel B. Observable characteristics of the final price-modeling sample and other KG listings</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Characteristic</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Final price-modeling sample (N=521)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Other KG listings (N=6165)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Difference (final - other)</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>SMD (final vs other)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Application-domain links per listing</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Source-industry links per listing</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>0.142</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Share linked to multiple application domains</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>0.337</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Share linked to multiple source industries</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Supplier listing breadth in the full KG: mean</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>80.94199999999999</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>282.901</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>-201.959</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>-1.001</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Supplier listing breadth in the full KG: median</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>188</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>-164</v>
+      </c>
+      <c r="E16" s="21" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -831,55 +1206,55 @@
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Obs</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>P25</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P50</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>P75</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>heat_news</t>
         </is>
@@ -893,10 +1268,10 @@
       <c r="D2" s="4" t="n">
         <v>3.907</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
@@ -909,8 +1284,8 @@
         <v>11.374</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>heat_total</t>
         </is>
@@ -924,10 +1299,10 @@
       <c r="D3" s="4" t="n">
         <v>13.197</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
@@ -940,8 +1315,8 @@
         <v>38.799</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>heat_web</t>
         </is>
@@ -955,10 +1330,10 @@
       <c r="D4" s="4" t="n">
         <v>5.716</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
@@ -971,8 +1346,8 @@
         <v>18.148</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>heat_weixin</t>
         </is>
@@ -986,10 +1361,10 @@
       <c r="D5" s="4" t="n">
         <v>3.85</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
@@ -1002,8 +1377,8 @@
         <v>10.923</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
@@ -1033,8 +1408,8 @@
         <v>4.771</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>HHI_proxy</t>
         </is>
@@ -1060,305 +1435,45 @@
       <c r="H7" s="4" t="n">
         <v>0.053</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>521</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="7" t="n">
         <v>21.48</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>14.797</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>29.027</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="7" t="n">
         <v>34.721</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="7" t="n">
         <v>39.927</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Entity level</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>prod_ppr_expected_heat_total_struct</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Topology-only product-to-application demand exposure from heterogeneous-graph PPR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>prod_ppr_expected_heat_total_tele</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Heat-teleport product-to-application demand exposure from heterogeneous-graph PPR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>prod_ppr_app_entropy</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Entropy of the product-level PPR application posterior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>prod_ppr_src_entropy</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Entropy of the product-level PPR source-industry posterior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>prod_ppr_app_top1_prob / prod_ppr_src_top1_prob</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Top-1 concentration probabilities for application and source PPR posteriors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>prod_mp_ppr_expected_heat_total_struct</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>MPPR</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Topology-only product-level demand exposure aggregated from meta-path-constrained PPR posteriors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>prod_mp_ppr_expected_heat_total_tele</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>MPPR</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Heat-teleport product-level demand exposure aggregated from meta-path-constrained PPR posteriors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>prod_mp_ppr_app_entropy</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>MPPR</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Entropy of the product-level MPPR application posterior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>prod_mp_ppr_src_entropy</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>MPPR</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Entropy of the product-level MPPR source-industry posterior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>prod_mp_ppr_app_top1_prob / prod_mp_ppr_src_top1_prob</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>MPPR</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Top-1 concentration probabilities for application and source MPPR posteriors.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1366,291 +1481,263 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40.16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Entity level</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Features</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>R²</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>prod_ppr_expected_heat_total_struct</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Topology-only product-to-application demand exposure from heterogeneous-graph PPR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>prod_ppr_expected_heat_total_tele</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>PPR</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
-        <v>521</v>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>prod_ppr_expected_heat_total; prod_ppr_app_entropy; prod_ppr_src_entropy; prod_ppr_app_top1_prob; prod_ppr_src_top1_prob</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>1.239</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Heat-teleport product-to-application demand exposure from heterogeneous-graph PPR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>prod_ppr_app_entropy</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Entropy of the product-level PPR application posterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>prod_ppr_src_entropy</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Entropy of the product-level PPR source-industry posterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>prod_ppr_app_top1_prob / prod_ppr_src_top1_prob</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Top-1 concentration probabilities for application and source PPR posteriors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>prod_mp_ppr_expected_heat_total_struct</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>521</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>prod_mp_ppr_expected_heat_total; prod_mp_ppr_app_entropy; prod_mp_ppr_src_entropy; prod_mp_ppr_app_top1_prob; prod_mp_ppr_src_top1_prob</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1.234</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1.647</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Supplier</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>ppr_expected_heat_total; ppr_app_entropy; ppr_src_entropy; ppr_app_top1_prob; ppr_src_top1_prob</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>-0.182</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1.598</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>2.064</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Supplier</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Topology-only product-level demand exposure aggregated from meta-path-constrained PPR posteriors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>prod_mp_ppr_expected_heat_total_tele</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>mp_ppr_expected_heat_total; mp_ppr_app_entropy; mp_ppr_src_entropy; mp_ppr_app_top1_prob; mp_ppr_src_top1_prob</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-0.172</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1.603</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>2.056</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Src</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>ppr_expected_heat_total; ppr_app_entropy; ppr_app_top1_prob</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1.013</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1.326</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Src</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Heat-teleport product-level demand exposure aggregated from meta-path-constrained PPR posteriors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>prod_mp_ppr_app_entropy</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>mp_ppr_expected_heat_total; mp_ppr_app_entropy; mp_ppr_app_top1_prob</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1.303</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>PPR</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>ppr_src_entropy; ppr_src_top1_prob; heat_total</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1.118</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1.355</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Entropy of the product-level MPPR application posterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>prod_mp_ppr_src_entropy</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>mp_ppr_src_entropy; mp_ppr_sup_entropy; mp_ppr_src_top1_prob; mp_ppr_sup_top1_prob; heat_total</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-0.132</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1.113</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1.353</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Entropy of the product-level MPPR source-industry posterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>prod_mp_ppr_app_top1_prob / prod_mp_ppr_src_top1_prob</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>MPPR</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Top-1 concentration probabilities for application and source MPPR posteriors.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1658,81 +1745,375 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Entity level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>prod_ppr_expected_heat_total; prod_ppr_app_entropy; prod_ppr_src_entropy; prod_ppr_app_top1_prob; prod_ppr_src_top1_prob</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>MPPR</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>prod_mp_ppr_expected_heat_total; prod_mp_ppr_app_entropy; prod_mp_ppr_src_entropy; prod_mp_ppr_app_top1_prob; prod_mp_ppr_src_top1_prob</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1.647</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ppr_expected_heat_total; ppr_app_entropy; ppr_src_entropy; ppr_app_top1_prob; ppr_src_top1_prob</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>-0.182</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1.598</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>2.064</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MPPR</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>mp_ppr_expected_heat_total; mp_ppr_app_entropy; mp_ppr_src_entropy; mp_ppr_app_top1_prob; mp_ppr_src_top1_prob</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-0.172</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ppr_expected_heat_total; ppr_app_entropy; ppr_app_top1_prob</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1.326</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>MPPR</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>mp_ppr_expected_heat_total; mp_ppr_app_entropy; mp_ppr_app_top1_prob</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1.303</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PPR</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ppr_src_entropy; ppr_src_top1_prob; heat_total</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1.355</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>MPPR</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>mp_ppr_src_entropy; mp_ppr_sup_entropy; mp_ppr_src_top1_prob; mp_ppr_sup_top1_prob; heat_total</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>-0.132</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1.353</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Entity level</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Structural mean</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Heat-biased mean</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mean Δ</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Consistency (r / ρ)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Structural assoc. (ρ / slope)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Heat-biased assoc. (ρ / slope)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>PPR</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="3" t="n">
         <v>521</v>
       </c>
       <c r="D2" s="4" t="n">
@@ -1744,34 +2125,34 @@
       <c r="F2" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>0.993 / 0.978</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>0.193 / 0.030</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>0.160 / 0.035</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="3" t="n">
         <v>521</v>
       </c>
       <c r="D3" s="4" t="n">
@@ -1783,34 +2164,34 @@
       <c r="F3" s="4" t="n">
         <v>0.352</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>0.987 / 0.978</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>0.238 / 0.019</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>0.264 / 0.031</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>PPR</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="3" t="n">
         <v>86</v>
       </c>
       <c r="D4" s="4" t="n">
@@ -1822,34 +2203,34 @@
       <c r="F4" s="4" t="n">
         <v>1.554</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>0.983 / 0.979</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>0.081 / 0.007</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>0.066 / 0.009</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="3" t="n">
         <v>86</v>
       </c>
       <c r="D5" s="4" t="n">
@@ -1861,34 +2242,34 @@
       <c r="F5" s="4" t="n">
         <v>0.699</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>0.996 / 0.989</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>0.064 / 0.013</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>0.038 / 0.012</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>PPR</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="3" t="n">
         <v>119</v>
       </c>
       <c r="D6" s="4" t="n">
@@ -1900,63 +2281,65 @@
       <c r="F6" s="4" t="n">
         <v>2.927</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>0.978 / 0.976</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>-0.159 / -0.025</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>-0.106 / -0.020</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>15.793</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="7" t="n">
         <v>17.157</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="7" t="n">
         <v>1.364</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>0.999 / 0.995</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>-0.242 / -0.037</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>-0.247 / -0.044</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1964,13 +2347,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="27.92" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1978,68 +2361,62 @@
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Model specification</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SMAPE</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Panel A. Independent full-sample fit</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr"/>
-      <c r="C2" s="6" t="inlineStr"/>
-      <c r="D2" s="6" t="inlineStr"/>
-      <c r="E2" s="6" t="inlineStr"/>
-      <c r="F2" s="6" t="inlineStr"/>
-      <c r="G2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Intercept only</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
@@ -2055,13 +2432,13 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
@@ -2082,13 +2459,13 @@
         <v>0.409</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
@@ -2109,13 +2486,13 @@
         <v>0.742</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
@@ -2136,13 +2513,13 @@
         <v>0.825</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
@@ -2163,13 +2540,13 @@
         <v>0.586</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
@@ -2190,13 +2567,13 @@
         <v>0.906</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
@@ -2217,13 +2594,13 @@
         <v>0.985</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
@@ -2244,26 +2621,20 @@
         <v>0.9379999999999999</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Panel B. Conditional specifications</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
@@ -2284,13 +2655,13 @@
         <v>0.409</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE</t>
         </is>
@@ -2311,13 +2682,13 @@
         <v>0.415</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE+ App FE</t>
         </is>
@@ -2338,13 +2709,13 @@
         <v>0.429</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product</t>
         </is>
@@ -2365,13 +2736,13 @@
         <v>0.524</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Supply</t>
         </is>
@@ -2392,13 +2763,13 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Demand</t>
         </is>
@@ -2419,13 +2790,13 @@
         <v>0.528</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Market</t>
         </is>
@@ -2446,35 +2817,41 @@
         <v>0.534</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Full model</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Full: Supplier FE + Src FE + App FE + Product + Supply + Demand + Market</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="7" t="n">
         <v>0.66</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="7" t="n">
         <v>0.646</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="7" t="n">
         <v>0.988</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="7" t="n">
         <v>1.078</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>0.539</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="2">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2482,367 +2859,362 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="28.64" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Single-block R²</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R² without component</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ΔR²</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapley R² contribution</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Panel A. Single-block full-sample fit</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr"/>
-      <c r="C2" s="6" t="inlineStr"/>
-      <c r="D2" s="6" t="inlineStr"/>
-      <c r="E2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="4" t="n">
         <v>0.762</v>
       </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr"/>
+      <c r="E3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="4" t="n">
         <v>0.391</v>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="9" t="inlineStr"/>
+      <c r="E4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="4" t="n">
         <v>0.343</v>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="4" t="n">
         <v>0.548</v>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="4" t="n">
         <v>0.044</v>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="4" t="n">
         <v>0.02</v>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="4" t="n">
         <v>0.047</v>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Panel B. Drop-one from full model</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="10" t="n">
         <v>0.594</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>0.066</v>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="10" t="n">
         <v>0.62</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>0.039</v>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="10" t="n">
         <v>0.76</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="9" t="inlineStr"/>
+      <c r="C14" s="10" t="n">
         <v>0.771</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>-0.112</v>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="4" t="n">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="10" t="n">
         <v>0.67</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>-0.011</v>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="4" t="n">
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="10" t="n">
         <v>0.66</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="D16" s="4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="4" t="n">
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="10" t="n">
         <v>0.668</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Panel C. Shapley (full sample)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
       <c r="E19" s="4" t="n">
         <v>0.341</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr"/>
       <c r="E20" s="4" t="n">
         <v>0.103</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
       <c r="E21" s="4" t="n">
         <v>0.064</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
       <c r="E22" s="4" t="n">
         <v>0.145</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
       <c r="E23" s="4" t="n">
         <v>0.001</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr"/>
       <c r="E24" s="4" t="n">
         <v>0.004</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr"/>
+      <c r="B25" s="11" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="4" t="n">
+      <c r="D25" s="11" t="inlineStr"/>
+      <c r="E25" s="7" t="n">
         <v>0.002</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A18:E18"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2850,13 +3222,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="30.08" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2864,626 +3236,620 @@
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SMAPE</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Panel A. Independent K-fold fit</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr"/>
-      <c r="C2" s="6" t="inlineStr"/>
-      <c r="D2" s="6" t="inlineStr"/>
-      <c r="E2" s="6" t="inlineStr"/>
-      <c r="F2" s="6" t="inlineStr"/>
-      <c r="G2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Intercept only</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>-0.026 (0.033)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>1.333 (0.108)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>1.691 (0.167)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>2.651 (0.682)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>0.997 (0.044)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>0.502 (0.116)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>0.695 (0.074)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>1.167 (0.159)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>1.666 (0.560)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>0.535 (0.036)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>0.227 (0.028)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>1.061 (0.079)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>1.470 (0.161)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>2.271 (0.571)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>0.813 (0.029)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>0.152 (0.090)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>1.183 (0.075)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>1.531 (0.127)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>2.024 (0.369)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>0.911 (0.042)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>0.432 (0.108)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>0.816 (0.046)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>1.243 (0.069)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1.737 (0.372)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>0.638 (0.049)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>0.457 (0.054)</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>0.796 (0.070)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>1.227 (0.121)</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>1.798 (0.634)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>0.621 (0.037)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>0.021 (0.027)</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>1.235 (0.112)</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>1.656 (0.195)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>2.922 (0.729)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>0.911 (0.050)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>-0.015 (0.052)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>1.320 (0.098)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>1.680 (0.150)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>2.655 (0.636)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>0.989 (0.042)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>0.009 (0.053)</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>1.269 (0.097)</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>1.662 (0.164)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>2.698 (0.426)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>0.944 (0.044)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Panel B. Conditional additions (K-fold)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>0.502 (0.116)</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>0.695 (0.074)</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>1.167 (0.159)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>1.666 (0.560)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>0.535 (0.036)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>0.481 (0.127)</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>0.739 (0.087)</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>1.190 (0.176)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>1.918 (0.810)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>0.573 (0.035)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>0.485 (0.059)</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>0.775 (0.080)</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>1.197 (0.150)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>1.695 (0.548)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>0.609 (0.043)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>0.461 (0.108)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>0.791 (0.042)</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>1.209 (0.068)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>1.662 (0.327)</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>0.623 (0.045)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>0.481 (0.055)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>0.779 (0.067)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>1.200 (0.120)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>1.718 (0.584)</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>0.612 (0.036)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Supply</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>0.458 (0.110)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>0.792 (0.042)</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>1.213 (0.067)</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>1.679 (0.338)</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>0.624 (0.046)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>0.478 (0.056)</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>0.781 (0.069)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>1.202 (0.121)</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>1.728 (0.588)</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>0.614 (0.037)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Supply + Demand</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>0.456 (0.109)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>0.794 (0.043)</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>1.216 (0.069)</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>1.678 (0.332)</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>0.625 (0.046)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>0.477 (0.057)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>0.782 (0.069)</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>1.204 (0.121)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>1.726 (0.584)</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>0.614 (0.038)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Supply + Demand + Market</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>0.455 (0.110)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>0.797 (0.044)</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>1.216 (0.070)</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>1.693 (0.345)</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>0.627 (0.046)</t>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>0.476 (0.058)</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>0.787 (0.071)</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>1.205 (0.122)</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>1.754 (0.613)</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>0.619 (0.039)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="2">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3491,74 +3857,74 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Random K-fold R²</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Group K-fold R²</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Delta (Group–Random)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Group MAE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Group RMSE</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Supplier FE</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>0.502 (0.116)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>-0.790 (0.941)</t>
         </is>
@@ -3573,23 +3939,23 @@
         <v>1.786</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Src FE</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>0.481 (0.127)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>-0.827 (1.051)</t>
         </is>
@@ -3604,23 +3970,23 @@
         <v>1.792</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>App FE</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>0.485 (0.059)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>-0.768 (1.092)</t>
         </is>
@@ -3635,132 +4001,134 @@
         <v>1.719</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>0.461 (0.108)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>-2.028 (3.049)</t>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>0.481 (0.055)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>-0.210 (0.440)</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-2.489</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.71</v>
+        <v>1.205</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.381</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+        <v>1.545</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Supply</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>0.458 (0.110)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>-2.005 (3.017)</t>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>0.478 (0.056)</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>-0.210 (0.430)</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.463</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.705</v>
+        <v>1.205</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.374</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+        <v>1.548</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Supply + Demand</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>0.456 (0.109)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>-1.989 (2.995)</t>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>0.477 (0.057)</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>-0.223 (0.436)</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.444</v>
+        <v>-0.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.707</v>
+        <v>1.209</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.372</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+        <v>1.556</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Supplier FE + Src FE + App FE + Product + Supply + Demand + Market</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>0.455 (0.110)</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>-1.935 (2.929)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2.353</v>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>0.476 (0.058)</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>-0.214 (0.432)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1.551</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3768,46 +4136,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Entity level</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="4" t="n">
         <v>-0.173</v>
       </c>
       <c r="C2" s="4" t="n">
@@ -3817,13 +4185,13 @@
         <v>2.056</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="4" t="n">
         <v>0.043</v>
       </c>
       <c r="C3" s="4" t="n">
@@ -3833,13 +4201,13 @@
         <v>1.288</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>App</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="4" t="n">
         <v>-0.138</v>
       </c>
       <c r="C4" s="4" t="n">
@@ -3849,8 +4217,8 @@
         <v>1.356</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
@@ -3858,15 +4226,17 @@
       <c r="B5" s="7" t="n">
         <v>0.163</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="7" t="n">
         <v>1.094</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>1.521</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3874,47 +4244,47 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Consistency (r / ρ)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Structural assoc. (ρ / slope)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Heat-biased assoc. (ρ / slope)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PPR</t>
         </is>
@@ -3922,49 +4292,51 @@
       <c r="B2" s="3" t="n">
         <v>521</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>0.993 / 0.978</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>0.193 / 0.030</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>0.160 / 0.035</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>MPPR</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="6" t="n">
         <v>521</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>0.987 / 0.978</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>0.238 / 0.019</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>0.264 / 0.031</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3972,35 +4344,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="35.84" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Audit/source basis</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>External KG API DataProduct universe</t>
         </is>
@@ -4008,14 +4380,14 @@
       <c r="B2" s="3" t="n">
         <v>6686</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Unique API DataProduct nodes in the anonymized Neo4j export after cleaning, de-duplication, anonymization, and KG instantiation.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Raw price-file rows</t>
         </is>
@@ -4023,14 +4395,14 @@
       <c r="B3" s="3" t="n">
         <v>559</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Rows in the raw price file used for price cleaning.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Unique product-supplier pairs in raw price file</t>
         </is>
@@ -4038,14 +4410,14 @@
       <c r="B4" s="3" t="n">
         <v>555</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Product name and supplier name are used as the uniqueness criterion.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Zero-price records removed</t>
         </is>
@@ -4053,14 +4425,14 @@
       <c r="B5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Records with price = 0; excluded because they do not represent positive paid API posted quotes.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Upper-tail observations removed</t>
         </is>
@@ -4068,14 +4440,14 @@
       <c r="B6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Records priced at 300 RMB per call or above.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Final price-modeling sample</t>
         </is>
@@ -4083,19 +4455,19 @@
       <c r="B7" s="3" t="n">
         <v>521</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Unique API products with positive normalized posted prices after cleaning.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Final sample matched back to KG</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>521</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4105,7 +4477,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4113,151 +4487,153 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="26.48" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Relation (r)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Schema (Start → End)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>#Edges</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>#Start</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>#End</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Start out-degree (mean; P25/P50/P75; max)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>End in-degree (mean; P25/P50/P75; max)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>provide_data</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Supplier → DataProduct</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>521</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="4" t="n">
         <v>521</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>6.058; 1/2/4; 145</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>1.000; 1/1/1; 1</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>source_industry</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>src_IndustryCategory → DataProduct</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>605</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="4" t="n">
         <v>521</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>5.084; 1/1/2; 155</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>1.161; 1/1/1; 15</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>applied_to</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>DataProduct → app_IndustryCategory</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="7" t="n">
         <v>764</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="7" t="n">
         <v>521</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>1.466; 1/1/2; 6</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>4.775; 1/1/3; 203</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
+++ b/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>External KG API DataProduct universe</t>
+          <t>Broader KG API-listing universe</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Unique API DataProduct nodes in the anonymized Neo4j export after cleaning, de-duplication, anonymization, and KG instantiation.</t>
+          <t>Unique API listings retained after cleaning and de-duplication for KG construction.</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Zero-price records removed</t>
+          <t>Zero-price listings removed</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -4434,7 +4434,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Upper-tail observations removed</t>
+          <t>Upper-tail listings removed</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Unique API products with positive normalized posted prices after cleaning.</t>
+          <t>Unique API listings with positive normalized posted prices after cleaning.</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Final modeling records matched to the KG through anonymized product and supplier labels.</t>
+          <t>Paid API listings with positive normalized posted prices after cleaning.</t>
         </is>
       </c>
     </row>

--- a/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
+++ b/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Supplier FE + Src FE+ App FE</t>
+          <t>Supplier FE + Src FE + App FE</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Paid API listings with positive normalized posted prices after cleaning.</t>
+          <t>Final modeling API listings matched to the KG through anonymized product and supplier labels.</t>
         </is>
       </c>
     </row>

--- a/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
+++ b/result_kg_reproduce/table_merge/Paper_All_Tables_Merged.xlsx
@@ -705,7 +705,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.72" customWidth="1" min="1" max="1"/>
-    <col width="35.84" customWidth="1" min="2" max="2"/>
+    <col width="52.4" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -734,7 +734,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Products (with price)</t>
+          <t>DataProduct nodes in the final priced sample</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Suppliers (connected to priced products)</t>
+          <t>Supplier nodes connected to final-sample DataProduct nodes</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>src industries (connected to priced products)</t>
+          <t>src_IndustryCategory nodes connected to final-sample DataProduct nodes</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>app industries (connected to priced products)</t>
+          <t>app_IndustryCategory nodes connected to final-sample DataProduct nodes</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
